--- a/ig/improve-doc/all-profiles.xlsx
+++ b/ig/improve-doc/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T15:55:45+00:00</t>
+    <t>2024-11-26T12:51:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/improve-doc/all-profiles.xlsx
+++ b/ig/improve-doc/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-26T12:51:17+00:00</t>
+    <t>2024-11-26T14:12:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/improve-doc/all-profiles.xlsx
+++ b/ig/improve-doc/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-26T14:12:54+00:00</t>
+    <t>2024-12-02T10:46:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/improve-doc/all-profiles.xlsx
+++ b/ig/improve-doc/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7329" uniqueCount="754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7329" uniqueCount="756">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-02T10:46:43+00:00</t>
+    <t>2024-12-02T16:50:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -842,7 +842,7 @@
     <t>CodeSystem.url</t>
   </si>
   <si>
-    <t>L'ANS est autorité sur les URLs de type https://mos.esante.gouv.fr/fhir/CodeSystem/* et https://smt.esante.gouv.fr/fhir/CodeSystem/*</t>
+    <t>L'URL doit être de type https://smt.esante.gouv.fr/fhir/CodeSystem/*</t>
   </si>
   <si>
     <t>An absolute URI that is used to identify this code system when it is referenced in a specification, model, design or an instance; also called its canonical identifier. This SHOULD be globally unique and SHOULD be a literal address at which at which an authoritative instance of this code system is (or will be) published. This URL can be the target of a canonical reference. It SHALL remain the same when the code system is stored on different servers. This is used in [Coding](http://hl7.org/fhir/datatypes.html#Coding).system.</t>
@@ -856,6 +856,10 @@
     <t>Allows the code system to be referenced by a single globally unique identifier.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ans-cs-url-regex:url matches smt regex {$this.matches('https:\/\/smt.esante.gouv.fr\/fhir\/CodeSystem\/[a-z0-9]+(?:-[a-z0-9]+)*')}</t>
+  </si>
+  <si>
     <t>CodeSystem.identifier</t>
   </si>
   <si>
@@ -1661,13 +1665,17 @@
     <t>ValueSet.url</t>
   </si>
   <si>
-    <t>L'ANS est autorité sur les URLs de type https://mos.esante.gouv.fr/fhir/ValueSet/* et https://smt.esante.gouv.fr/fhir/ValueSet/*</t>
+    <t>URL au format https://smt.esante.gouv.fr/fhir/ValueSet/*</t>
   </si>
   <si>
     <t>An absolute URI that is used to identify this value set when it is referenced in a specification, model, design or an instance; also called its canonical identifier. This SHOULD be globally unique and SHOULD be a literal address at which at which an authoritative instance of this value set is (or will be) published. This URL can be the target of a canonical reference. It SHALL remain the same when the value set is stored on different servers.</t>
   </si>
   <si>
     <t>Allows the value set to be referenced by a single globally unique identifier.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ans-vs-url-regex:url matches smt regex {$this.matches('https:\/\/smt.esante.gouv.fr\/fhir\/ValueSet\/[a-z0-9]+(?:-[a-z0-9]+)*')}</t>
   </si>
   <si>
     <t>ValueSet.identifier</t>
@@ -2989,7 +2997,7 @@
         <v>2</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="68">
@@ -2997,7 +3005,7 @@
         <v>4</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="69">
@@ -3011,7 +3019,7 @@
         <v>7</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="71">
@@ -3019,7 +3027,7 @@
         <v>9</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="72">
@@ -3073,7 +3081,7 @@
         <v>21</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="79">
@@ -3109,7 +3117,7 @@
         <v>29</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="84">
@@ -3117,7 +3125,7 @@
         <v>31</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="85">
@@ -3149,7 +3157,7 @@
         <v>2</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
     </row>
     <row r="89">
@@ -3157,7 +3165,7 @@
         <v>4</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="90">
@@ -3171,7 +3179,7 @@
         <v>7</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
     </row>
     <row r="92">
@@ -3299,7 +3307,7 @@
         <v>37</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
     </row>
     <row r="109">
@@ -3315,7 +3323,7 @@
         <v>2</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
     </row>
     <row r="111">
@@ -3323,7 +3331,7 @@
         <v>4</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
     </row>
     <row r="112">
@@ -3337,7 +3345,7 @@
         <v>7</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
     </row>
     <row r="114">
@@ -3465,7 +3473,7 @@
         <v>37</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
     </row>
   </sheetData>
@@ -7799,7 +7807,7 @@
         <v>75</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>103</v>
+        <v>269</v>
       </c>
     </row>
     <row r="42">
@@ -7807,10 +7815,10 @@
         <v>109</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -7833,19 +7841,19 @@
         <v>120</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P42" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q42" t="s" s="2">
         <v>75</v>
@@ -7894,7 +7902,7 @@
         <v>75</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>76</v>
@@ -7914,10 +7922,10 @@
         <v>109</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
@@ -7943,13 +7951,13 @@
         <v>83</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P43" s="2"/>
       <c r="Q43" t="s" s="2">
@@ -7999,7 +8007,7 @@
         <v>75</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>76</v>
@@ -8019,10 +8027,10 @@
         <v>109</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
@@ -8048,16 +8056,16 @@
         <v>83</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P44" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q44" t="s" s="2">
         <v>75</v>
@@ -8106,7 +8114,7 @@
         <v>75</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>76</v>
@@ -8115,7 +8123,7 @@
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>103</v>
@@ -8126,10 +8134,10 @@
         <v>109</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -8155,13 +8163,13 @@
         <v>83</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P45" s="2"/>
       <c r="Q45" t="s" s="2">
@@ -8211,7 +8219,7 @@
         <v>75</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>76</v>
@@ -8231,10 +8239,10 @@
         <v>109</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -8260,13 +8268,13 @@
         <v>189</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P46" s="2"/>
       <c r="Q46" t="s" s="2">
@@ -8295,10 +8303,10 @@
         <v>173</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AA46" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AB46" t="s" s="2">
         <v>75</v>
@@ -8316,7 +8324,7 @@
         <v>75</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>82</v>
@@ -8336,10 +8344,10 @@
         <v>109</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -8362,19 +8370,19 @@
         <v>120</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P47" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q47" t="s" s="2">
         <v>75</v>
@@ -8423,7 +8431,7 @@
         <v>75</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>76</v>
@@ -8443,14 +8451,14 @@
         <v>109</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" t="s" s="2">
@@ -8472,13 +8480,13 @@
         <v>238</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P48" s="2"/>
       <c r="Q48" t="s" s="2">
@@ -8528,7 +8536,7 @@
         <v>75</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>76</v>
@@ -8548,14 +8556,14 @@
         <v>109</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" t="s" s="2">
@@ -8577,16 +8585,16 @@
         <v>83</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P49" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q49" t="s" s="2">
         <v>75</v>
@@ -8635,7 +8643,7 @@
         <v>75</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>76</v>
@@ -8655,10 +8663,10 @@
         <v>109</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -8684,13 +8692,13 @@
         <v>100</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P50" s="2"/>
       <c r="Q50" t="s" s="2">
@@ -8740,7 +8748,7 @@
         <v>75</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>76</v>
@@ -8760,14 +8768,14 @@
         <v>109</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" t="s" s="2">
@@ -8786,16 +8794,16 @@
         <v>75</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P51" s="2"/>
       <c r="Q51" t="s" s="2">
@@ -8845,7 +8853,7 @@
         <v>75</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>76</v>
@@ -8865,10 +8873,10 @@
         <v>109</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -8891,19 +8899,19 @@
         <v>120</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P52" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q52" t="s" s="2">
         <v>75</v>
@@ -8952,7 +8960,7 @@
         <v>75</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>76</v>
@@ -8972,10 +8980,10 @@
         <v>109</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -8998,16 +9006,16 @@
         <v>120</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P53" s="2"/>
       <c r="Q53" t="s" s="2">
@@ -9036,10 +9044,10 @@
         <v>165</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AA53" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AB53" t="s" s="2">
         <v>75</v>
@@ -9057,7 +9065,7 @@
         <v>75</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>76</v>
@@ -9077,10 +9085,10 @@
         <v>109</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -9103,16 +9111,16 @@
         <v>75</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P54" s="2"/>
       <c r="Q54" t="s" s="2">
@@ -9162,7 +9170,7 @@
         <v>75</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>76</v>
@@ -9182,14 +9190,14 @@
         <v>109</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" t="s" s="2">
@@ -9208,19 +9216,19 @@
         <v>75</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P55" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q55" t="s" s="2">
         <v>75</v>
@@ -9269,7 +9277,7 @@
         <v>75</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>76</v>
@@ -9289,10 +9297,10 @@
         <v>109</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -9315,16 +9323,16 @@
         <v>120</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P56" s="2"/>
       <c r="Q56" t="s" s="2">
@@ -9374,7 +9382,7 @@
         <v>75</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>76</v>
@@ -9394,10 +9402,10 @@
         <v>109</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -9420,16 +9428,16 @@
         <v>120</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P57" s="2"/>
       <c r="Q57" t="s" s="2">
@@ -9479,7 +9487,7 @@
         <v>75</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>76</v>
@@ -9499,10 +9507,10 @@
         <v>109</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -9528,13 +9536,13 @@
         <v>189</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P58" s="2"/>
       <c r="Q58" t="s" s="2">
@@ -9563,10 +9571,10 @@
         <v>173</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AA58" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AB58" t="s" s="2">
         <v>75</v>
@@ -9584,7 +9592,7 @@
         <v>75</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>76</v>
@@ -9604,14 +9612,14 @@
         <v>109</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" t="s" s="2">
@@ -9630,16 +9638,16 @@
         <v>120</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P59" s="2"/>
       <c r="Q59" t="s" s="2">
@@ -9689,7 +9697,7 @@
         <v>75</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>76</v>
@@ -9709,10 +9717,10 @@
         <v>109</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -9735,16 +9743,16 @@
         <v>120</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P60" s="2"/>
       <c r="Q60" t="s" s="2">
@@ -9794,7 +9802,7 @@
         <v>75</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>76</v>
@@ -9814,10 +9822,10 @@
         <v>109</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -9843,10 +9851,10 @@
         <v>189</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" s="2"/>
@@ -9876,10 +9884,10 @@
         <v>173</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AA61" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AB61" t="s" s="2">
         <v>75</v>
@@ -9897,7 +9905,7 @@
         <v>75</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>82</v>
@@ -9917,10 +9925,10 @@
         <v>109</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
@@ -9943,16 +9951,16 @@
         <v>120</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P62" s="2"/>
       <c r="Q62" t="s" s="2">
@@ -10002,7 +10010,7 @@
         <v>75</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>76</v>
@@ -10022,10 +10030,10 @@
         <v>109</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
@@ -10048,16 +10056,16 @@
         <v>120</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P63" s="2"/>
       <c r="Q63" t="s" s="2">
@@ -10107,7 +10115,7 @@
         <v>75</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>76</v>
@@ -10127,10 +10135,10 @@
         <v>109</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -10153,16 +10161,16 @@
         <v>120</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P64" s="2"/>
       <c r="Q64" t="s" s="2">
@@ -10212,7 +10220,7 @@
         <v>75</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>76</v>
@@ -10232,10 +10240,10 @@
         <v>109</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -10335,10 +10343,10 @@
         <v>109</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
@@ -10440,14 +10448,14 @@
         <v>109</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" t="s" s="2">
@@ -10469,10 +10477,10 @@
         <v>88</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O67" t="s" s="2">
         <v>137</v>
@@ -10527,7 +10535,7 @@
         <v>75</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>76</v>
@@ -10547,10 +10555,10 @@
         <v>109</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -10576,10 +10584,10 @@
         <v>189</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" s="2"/>
@@ -10630,7 +10638,7 @@
         <v>75</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>82</v>
@@ -10650,10 +10658,10 @@
         <v>109</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -10679,10 +10687,10 @@
         <v>83</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" s="2"/>
@@ -10733,7 +10741,7 @@
         <v>75</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>76</v>
@@ -10753,10 +10761,10 @@
         <v>109</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -10782,10 +10790,10 @@
         <v>189</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" s="2"/>
@@ -10815,10 +10823,10 @@
         <v>173</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA70" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AB70" t="s" s="2">
         <v>75</v>
@@ -10836,7 +10844,7 @@
         <v>75</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>82</v>
@@ -10856,10 +10864,10 @@
         <v>109</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -10885,10 +10893,10 @@
         <v>83</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" s="2"/>
@@ -10939,7 +10947,7 @@
         <v>75</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>82</v>
@@ -10959,10 +10967,10 @@
         <v>109</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -10985,13 +10993,13 @@
         <v>120</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" s="2"/>
@@ -11042,7 +11050,7 @@
         <v>75</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>76</v>
@@ -11062,10 +11070,10 @@
         <v>109</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -11165,10 +11173,10 @@
         <v>109</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -11270,14 +11278,14 @@
         <v>109</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" t="s" s="2">
@@ -11299,10 +11307,10 @@
         <v>88</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O75" t="s" s="2">
         <v>137</v>
@@ -11357,7 +11365,7 @@
         <v>75</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>76</v>
@@ -11377,10 +11385,10 @@
         <v>109</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -11406,10 +11414,10 @@
         <v>189</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" s="2"/>
@@ -11460,7 +11468,7 @@
         <v>75</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>82</v>
@@ -11480,10 +11488,10 @@
         <v>109</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -11509,10 +11517,10 @@
         <v>95</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" s="2"/>
@@ -11563,7 +11571,7 @@
         <v>75</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>76</v>
@@ -11583,10 +11591,10 @@
         <v>109</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -11612,10 +11620,10 @@
         <v>83</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" s="2"/>
@@ -11666,7 +11674,7 @@
         <v>75</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>76</v>
@@ -11686,10 +11694,10 @@
         <v>109</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -11715,10 +11723,10 @@
         <v>189</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" s="2"/>
@@ -11748,10 +11756,10 @@
         <v>173</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AA79" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AB79" t="s" s="2">
         <v>75</v>
@@ -11769,7 +11777,7 @@
         <v>75</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>82</v>
@@ -11789,10 +11797,10 @@
         <v>109</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -11815,16 +11823,16 @@
         <v>75</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P80" s="2"/>
       <c r="Q80" t="s" s="2">
@@ -11874,7 +11882,7 @@
         <v>75</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>76</v>
@@ -11894,10 +11902,10 @@
         <v>109</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -11997,10 +12005,10 @@
         <v>109</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -12102,14 +12110,14 @@
         <v>109</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" t="s" s="2">
@@ -12131,10 +12139,10 @@
         <v>88</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O83" t="s" s="2">
         <v>137</v>
@@ -12189,7 +12197,7 @@
         <v>75</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>76</v>
@@ -12209,10 +12217,10 @@
         <v>109</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -12238,10 +12246,10 @@
         <v>189</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" s="2"/>
@@ -12292,7 +12300,7 @@
         <v>75</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>82</v>
@@ -12312,10 +12320,10 @@
         <v>109</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -12341,10 +12349,10 @@
         <v>83</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" s="2"/>
@@ -12395,7 +12403,7 @@
         <v>75</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>76</v>
@@ -12415,10 +12423,10 @@
         <v>109</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -12444,10 +12452,10 @@
         <v>83</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" s="2"/>
@@ -12498,7 +12506,7 @@
         <v>75</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>76</v>
@@ -12518,10 +12526,10 @@
         <v>109</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -12544,19 +12552,19 @@
         <v>75</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P87" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q87" t="s" s="2">
         <v>75</v>
@@ -12605,7 +12613,7 @@
         <v>75</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>76</v>
@@ -12625,10 +12633,10 @@
         <v>109</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -12728,10 +12736,10 @@
         <v>109</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -12833,14 +12841,14 @@
         <v>109</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F90" s="2"/>
       <c r="G90" t="s" s="2">
@@ -12862,10 +12870,10 @@
         <v>88</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O90" t="s" s="2">
         <v>137</v>
@@ -12920,7 +12928,7 @@
         <v>75</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>76</v>
@@ -12940,10 +12948,10 @@
         <v>109</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -12969,13 +12977,13 @@
         <v>189</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P91" s="2"/>
       <c r="Q91" t="s" s="2">
@@ -13025,7 +13033,7 @@
         <v>75</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>76</v>
@@ -13045,10 +13053,10 @@
         <v>109</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -13074,13 +13082,13 @@
         <v>161</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="P92" s="2"/>
       <c r="Q92" t="s" s="2">
@@ -13109,10 +13117,10 @@
         <v>165</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AA92" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AB92" t="s" s="2">
         <v>75</v>
@@ -13130,7 +13138,7 @@
         <v>75</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>76</v>
@@ -13150,10 +13158,10 @@
         <v>109</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -13179,10 +13187,10 @@
         <v>83</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" s="2"/>
@@ -13233,7 +13241,7 @@
         <v>75</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>82</v>
@@ -13253,10 +13261,10 @@
         <v>109</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -13279,13 +13287,13 @@
         <v>75</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" s="2"/>
@@ -13336,7 +13344,7 @@
         <v>75</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>76</v>
@@ -13356,10 +13364,10 @@
         <v>109</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
@@ -13459,10 +13467,10 @@
         <v>109</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
@@ -13564,14 +13572,14 @@
         <v>109</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F97" s="2"/>
       <c r="G97" t="s" s="2">
@@ -13593,10 +13601,10 @@
         <v>88</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O97" t="s" s="2">
         <v>137</v>
@@ -13651,7 +13659,7 @@
         <v>75</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>76</v>
@@ -13671,10 +13679,10 @@
         <v>109</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -13700,10 +13708,10 @@
         <v>189</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" s="2"/>
@@ -13754,7 +13762,7 @@
         <v>75</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>82</v>
@@ -13774,10 +13782,10 @@
         <v>109</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -13800,13 +13808,13 @@
         <v>75</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" s="2"/>
@@ -13857,7 +13865,7 @@
         <v>75</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>82</v>
@@ -13877,10 +13885,10 @@
         <v>109</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -13906,10 +13914,10 @@
         <v>78</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" s="2"/>
@@ -13960,7 +13968,7 @@
         <v>75</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>76</v>
@@ -13977,13 +13985,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -14009,10 +14017,10 @@
         <v>78</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" s="2"/>
@@ -14063,7 +14071,7 @@
         <v>75</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>76</v>
@@ -14075,18 +14083,18 @@
         <v>75</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -14185,13 +14193,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -14288,13 +14296,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -14391,13 +14399,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -14496,13 +14504,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -14601,13 +14609,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -14706,13 +14714,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -14811,13 +14819,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -14916,13 +14924,13 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -15021,13 +15029,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B111" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C111" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="C111" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>172</v>
@@ -15126,13 +15134,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -15231,13 +15239,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -15336,13 +15344,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
@@ -15441,13 +15449,13 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" t="s" s="2">
@@ -15546,13 +15554,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" t="s" s="2">
@@ -15651,13 +15659,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" t="s" s="2">
@@ -15752,13 +15760,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B118" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C118" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="C118" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>214</v>
@@ -15859,13 +15867,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
@@ -15962,13 +15970,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
@@ -16065,13 +16073,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
@@ -16170,13 +16178,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
@@ -16273,13 +16281,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
@@ -16376,13 +16384,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
@@ -16481,13 +16489,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
@@ -16586,13 +16594,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" t="s" s="2">
@@ -16693,13 +16701,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D127" t="s" s="2">
         <v>252</v>
@@ -16724,7 +16732,7 @@
         <v>75</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M127" t="s" s="2">
         <v>254</v>
@@ -16798,13 +16806,13 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D128" t="s" s="2">
         <v>256</v>
@@ -16829,7 +16837,7 @@
         <v>75</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M128" t="s" s="2">
         <v>258</v>
@@ -16903,13 +16911,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" t="s" s="2">
@@ -17010,13 +17018,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -17042,16 +17050,16 @@
         <v>95</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O130" t="s" s="2">
         <v>267</v>
       </c>
       <c r="P130" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="Q130" t="s" s="2">
         <v>75</v>
@@ -17100,7 +17108,7 @@
         <v>75</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AH130" t="s" s="2">
         <v>76</v>
@@ -17112,18 +17120,18 @@
         <v>75</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>103</v>
+        <v>534</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
@@ -17146,19 +17154,19 @@
         <v>120</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="P131" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q131" t="s" s="2">
         <v>75</v>
@@ -17207,7 +17215,7 @@
         <v>75</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>76</v>
@@ -17224,13 +17232,13 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
@@ -17256,13 +17264,13 @@
         <v>83</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="P132" s="2"/>
       <c r="Q132" t="s" s="2">
@@ -17312,7 +17320,7 @@
         <v>75</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>76</v>
@@ -17329,13 +17337,13 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" t="s" s="2">
@@ -17361,16 +17369,16 @@
         <v>83</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="P133" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q133" t="s" s="2">
         <v>75</v>
@@ -17419,7 +17427,7 @@
         <v>75</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>76</v>
@@ -17428,7 +17436,7 @@
         <v>82</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>103</v>
@@ -17436,13 +17444,13 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" t="s" s="2">
@@ -17468,13 +17476,13 @@
         <v>83</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P134" s="2"/>
       <c r="Q134" t="s" s="2">
@@ -17524,7 +17532,7 @@
         <v>75</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AH134" t="s" s="2">
         <v>76</v>
@@ -17541,13 +17549,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" t="s" s="2">
@@ -17573,13 +17581,13 @@
         <v>189</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="P135" s="2"/>
       <c r="Q135" t="s" s="2">
@@ -17608,10 +17616,10 @@
         <v>173</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AA135" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AB135" t="s" s="2">
         <v>75</v>
@@ -17629,7 +17637,7 @@
         <v>75</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AH135" t="s" s="2">
         <v>82</v>
@@ -17646,13 +17654,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" t="s" s="2">
@@ -17675,19 +17683,19 @@
         <v>120</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="P136" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="Q136" t="s" s="2">
         <v>75</v>
@@ -17736,7 +17744,7 @@
         <v>75</v>
       </c>
       <c r="AG136" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AH136" t="s" s="2">
         <v>76</v>
@@ -17753,17 +17761,17 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F137" s="2"/>
       <c r="G137" t="s" s="2">
@@ -17785,13 +17793,13 @@
         <v>238</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="P137" s="2"/>
       <c r="Q137" t="s" s="2">
@@ -17841,7 +17849,7 @@
         <v>75</v>
       </c>
       <c r="AG137" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AH137" t="s" s="2">
         <v>76</v>
@@ -17858,17 +17866,17 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F138" s="2"/>
       <c r="G138" t="s" s="2">
@@ -17890,16 +17898,16 @@
         <v>83</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="P138" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="Q138" t="s" s="2">
         <v>75</v>
@@ -17948,7 +17956,7 @@
         <v>75</v>
       </c>
       <c r="AG138" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AH138" t="s" s="2">
         <v>76</v>
@@ -17965,13 +17973,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" t="s" s="2">
@@ -17997,13 +18005,13 @@
         <v>100</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P139" s="2"/>
       <c r="Q139" t="s" s="2">
@@ -18053,7 +18061,7 @@
         <v>75</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AH139" t="s" s="2">
         <v>76</v>
@@ -18070,17 +18078,17 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F140" s="2"/>
       <c r="G140" t="s" s="2">
@@ -18099,16 +18107,16 @@
         <v>75</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="P140" s="2"/>
       <c r="Q140" t="s" s="2">
@@ -18158,7 +18166,7 @@
         <v>75</v>
       </c>
       <c r="AG140" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AH140" t="s" s="2">
         <v>76</v>
@@ -18175,13 +18183,13 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" t="s" s="2">
@@ -18204,19 +18212,19 @@
         <v>120</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P141" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q141" t="s" s="2">
         <v>75</v>
@@ -18265,7 +18273,7 @@
         <v>75</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AH141" t="s" s="2">
         <v>76</v>
@@ -18282,13 +18290,13 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" t="s" s="2">
@@ -18311,16 +18319,16 @@
         <v>120</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="P142" s="2"/>
       <c r="Q142" t="s" s="2">
@@ -18349,10 +18357,10 @@
         <v>165</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AA142" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AB142" t="s" s="2">
         <v>75</v>
@@ -18370,7 +18378,7 @@
         <v>75</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>76</v>
@@ -18387,13 +18395,13 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" t="s" s="2">
@@ -18416,16 +18424,16 @@
         <v>120</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="P143" s="2"/>
       <c r="Q143" t="s" s="2">
@@ -18475,7 +18483,7 @@
         <v>75</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AH143" t="s" s="2">
         <v>76</v>
@@ -18492,13 +18500,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" t="s" s="2">
@@ -18521,16 +18529,16 @@
         <v>75</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="P144" s="2"/>
       <c r="Q144" t="s" s="2">
@@ -18580,7 +18588,7 @@
         <v>75</v>
       </c>
       <c r="AG144" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AH144" t="s" s="2">
         <v>76</v>
@@ -18597,17 +18605,17 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F145" s="2"/>
       <c r="G145" t="s" s="2">
@@ -18626,19 +18634,19 @@
         <v>75</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="P145" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Q145" t="s" s="2">
         <v>75</v>
@@ -18687,7 +18695,7 @@
         <v>75</v>
       </c>
       <c r="AG145" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AH145" t="s" s="2">
         <v>76</v>
@@ -18704,17 +18712,17 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="F146" s="2"/>
       <c r="G146" t="s" s="2">
@@ -18733,13 +18741,13 @@
         <v>75</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" s="2"/>
@@ -18790,7 +18798,7 @@
         <v>75</v>
       </c>
       <c r="AG146" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AH146" t="s" s="2">
         <v>76</v>
@@ -18807,13 +18815,13 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" t="s" s="2">
@@ -18910,13 +18918,13 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" t="s" s="2">
@@ -19015,17 +19023,17 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F149" s="2"/>
       <c r="G149" t="s" s="2">
@@ -19047,10 +19055,10 @@
         <v>88</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O149" t="s" s="2">
         <v>137</v>
@@ -19105,7 +19113,7 @@
         <v>75</v>
       </c>
       <c r="AG149" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AH149" t="s" s="2">
         <v>76</v>
@@ -19122,13 +19130,13 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" t="s" s="2">
@@ -19151,16 +19159,16 @@
         <v>120</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="P150" s="2"/>
       <c r="Q150" t="s" s="2">
@@ -19210,7 +19218,7 @@
         <v>75</v>
       </c>
       <c r="AG150" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AH150" t="s" s="2">
         <v>76</v>
@@ -19227,13 +19235,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" t="s" s="2">
@@ -19256,16 +19264,16 @@
         <v>120</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="P151" s="2"/>
       <c r="Q151" t="s" s="2">
@@ -19315,7 +19323,7 @@
         <v>75</v>
       </c>
       <c r="AG151" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AH151" t="s" s="2">
         <v>76</v>
@@ -19332,13 +19340,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" t="s" s="2">
@@ -19361,16 +19369,16 @@
         <v>120</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="P152" s="2"/>
       <c r="Q152" t="s" s="2">
@@ -19420,7 +19428,7 @@
         <v>75</v>
       </c>
       <c r="AG152" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AH152" t="s" s="2">
         <v>82</v>
@@ -19432,18 +19440,18 @@
         <v>75</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" t="s" s="2">
@@ -19540,13 +19548,13 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" t="s" s="2">
@@ -19645,17 +19653,17 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F155" s="2"/>
       <c r="G155" t="s" s="2">
@@ -19677,10 +19685,10 @@
         <v>88</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O155" t="s" s="2">
         <v>137</v>
@@ -19735,7 +19743,7 @@
         <v>75</v>
       </c>
       <c r="AG155" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AH155" t="s" s="2">
         <v>76</v>
@@ -19752,13 +19760,13 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" t="s" s="2">
@@ -19784,13 +19792,13 @@
         <v>95</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="P156" s="2"/>
       <c r="Q156" t="s" s="2">
@@ -19840,7 +19848,7 @@
         <v>75</v>
       </c>
       <c r="AG156" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AH156" t="s" s="2">
         <v>76</v>
@@ -19849,7 +19857,7 @@
         <v>82</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>103</v>
@@ -19857,13 +19865,13 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" t="s" s="2">
@@ -19889,13 +19897,13 @@
         <v>83</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="P157" s="2"/>
       <c r="Q157" t="s" s="2">
@@ -19945,7 +19953,7 @@
         <v>75</v>
       </c>
       <c r="AG157" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AH157" t="s" s="2">
         <v>76</v>
@@ -19962,13 +19970,13 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" t="s" s="2">
@@ -19991,16 +19999,16 @@
         <v>75</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="P158" s="2"/>
       <c r="Q158" t="s" s="2">
@@ -20050,7 +20058,7 @@
         <v>75</v>
       </c>
       <c r="AG158" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AH158" t="s" s="2">
         <v>76</v>
@@ -20059,7 +20067,7 @@
         <v>77</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AK158" t="s" s="2">
         <v>103</v>
@@ -20067,13 +20075,13 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" t="s" s="2">
@@ -20170,13 +20178,13 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D160" s="2"/>
       <c r="E160" t="s" s="2">
@@ -20275,17 +20283,17 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D161" s="2"/>
       <c r="E161" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F161" s="2"/>
       <c r="G161" t="s" s="2">
@@ -20307,10 +20315,10 @@
         <v>88</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O161" t="s" s="2">
         <v>137</v>
@@ -20365,7 +20373,7 @@
         <v>75</v>
       </c>
       <c r="AG161" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AH161" t="s" s="2">
         <v>76</v>
@@ -20382,13 +20390,13 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" t="s" s="2">
@@ -20414,13 +20422,13 @@
         <v>189</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="P162" s="2"/>
       <c r="Q162" t="s" s="2">
@@ -20470,7 +20478,7 @@
         <v>75</v>
       </c>
       <c r="AG162" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AH162" t="s" s="2">
         <v>82</v>
@@ -20487,13 +20495,13 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="D163" s="2"/>
       <c r="E163" t="s" s="2">
@@ -20519,13 +20527,13 @@
         <v>83</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="P163" s="2"/>
       <c r="Q163" t="s" s="2">
@@ -20575,7 +20583,7 @@
         <v>75</v>
       </c>
       <c r="AG163" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AH163" t="s" s="2">
         <v>76</v>
@@ -20592,13 +20600,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="D164" s="2"/>
       <c r="E164" t="s" s="2">
@@ -20621,16 +20629,16 @@
         <v>75</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P164" s="2"/>
       <c r="Q164" t="s" s="2">
@@ -20680,7 +20688,7 @@
         <v>75</v>
       </c>
       <c r="AG164" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AH164" t="s" s="2">
         <v>76</v>
@@ -20697,13 +20705,13 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D165" s="2"/>
       <c r="E165" t="s" s="2">
@@ -20800,13 +20808,13 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" t="s" s="2">
@@ -20905,17 +20913,17 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F167" s="2"/>
       <c r="G167" t="s" s="2">
@@ -20937,10 +20945,10 @@
         <v>88</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O167" t="s" s="2">
         <v>137</v>
@@ -20995,7 +21003,7 @@
         <v>75</v>
       </c>
       <c r="AG167" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AH167" t="s" s="2">
         <v>76</v>
@@ -21012,13 +21020,13 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" t="s" s="2">
@@ -21044,13 +21052,13 @@
         <v>189</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P168" s="2"/>
       <c r="Q168" t="s" s="2">
@@ -21100,7 +21108,7 @@
         <v>75</v>
       </c>
       <c r="AG168" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="AH168" t="s" s="2">
         <v>76</v>
@@ -21117,13 +21125,13 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" t="s" s="2">
@@ -21149,13 +21157,13 @@
         <v>161</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="P169" s="2"/>
       <c r="Q169" t="s" s="2">
@@ -21184,10 +21192,10 @@
         <v>165</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AA169" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AB169" t="s" s="2">
         <v>75</v>
@@ -21205,7 +21213,7 @@
         <v>75</v>
       </c>
       <c r="AG169" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AH169" t="s" s="2">
         <v>76</v>
@@ -21222,13 +21230,13 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D170" s="2"/>
       <c r="E170" t="s" s="2">
@@ -21254,10 +21262,10 @@
         <v>83</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" s="2"/>
@@ -21308,7 +21316,7 @@
         <v>75</v>
       </c>
       <c r="AG170" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AH170" t="s" s="2">
         <v>82</v>
@@ -21325,13 +21333,13 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="D171" s="2"/>
       <c r="E171" t="s" s="2">
@@ -21354,16 +21362,16 @@
         <v>120</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="P171" s="2"/>
       <c r="Q171" t="s" s="2">
@@ -21413,7 +21421,7 @@
         <v>75</v>
       </c>
       <c r="AG171" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AH171" t="s" s="2">
         <v>76</v>
@@ -21422,7 +21430,7 @@
         <v>77</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>103</v>
@@ -21430,13 +21438,13 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D172" s="2"/>
       <c r="E172" t="s" s="2">
@@ -21533,13 +21541,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D173" s="2"/>
       <c r="E173" t="s" s="2">
@@ -21638,17 +21646,17 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="D174" s="2"/>
       <c r="E174" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F174" s="2"/>
       <c r="G174" t="s" s="2">
@@ -21670,10 +21678,10 @@
         <v>88</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O174" t="s" s="2">
         <v>137</v>
@@ -21728,7 +21736,7 @@
         <v>75</v>
       </c>
       <c r="AG174" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AH174" t="s" s="2">
         <v>76</v>
@@ -21745,13 +21753,13 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D175" s="2"/>
       <c r="E175" t="s" s="2">
@@ -21777,10 +21785,10 @@
         <v>189</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" s="2"/>
@@ -21831,7 +21839,7 @@
         <v>75</v>
       </c>
       <c r="AG175" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AH175" t="s" s="2">
         <v>82</v>
@@ -21848,13 +21856,13 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="D176" s="2"/>
       <c r="E176" t="s" s="2">
@@ -21880,13 +21888,13 @@
         <v>189</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="P176" s="2"/>
       <c r="Q176" t="s" s="2">
@@ -21915,10 +21923,10 @@
         <v>173</v>
       </c>
       <c r="Z176" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA176" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AB176" t="s" s="2">
         <v>75</v>
@@ -21936,7 +21944,7 @@
         <v>75</v>
       </c>
       <c r="AG176" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AH176" t="s" s="2">
         <v>82</v>
@@ -21953,13 +21961,13 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="D177" s="2"/>
       <c r="E177" t="s" s="2">
@@ -21985,13 +21993,13 @@
         <v>83</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="P177" s="2"/>
       <c r="Q177" t="s" s="2">
@@ -22041,7 +22049,7 @@
         <v>75</v>
       </c>
       <c r="AG177" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AH177" t="s" s="2">
         <v>82</v>
@@ -22058,13 +22066,13 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="D178" s="2"/>
       <c r="E178" t="s" s="2">
@@ -22087,16 +22095,16 @@
         <v>120</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="P178" s="2"/>
       <c r="Q178" t="s" s="2">
@@ -22146,7 +22154,7 @@
         <v>75</v>
       </c>
       <c r="AG178" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="AH178" t="s" s="2">
         <v>76</v>
@@ -22155,7 +22163,7 @@
         <v>77</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AK178" t="s" s="2">
         <v>103</v>
@@ -22163,13 +22171,13 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="D179" s="2"/>
       <c r="E179" t="s" s="2">
@@ -22195,13 +22203,13 @@
         <v>78</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="P179" s="2"/>
       <c r="Q179" t="s" s="2">
@@ -22251,7 +22259,7 @@
         <v>75</v>
       </c>
       <c r="AG179" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AH179" t="s" s="2">
         <v>76</v>
@@ -22260,7 +22268,7 @@
         <v>77</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AK179" t="s" s="2">
         <v>103</v>
@@ -22268,13 +22276,13 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D180" s="2"/>
       <c r="E180" t="s" s="2">
@@ -22297,16 +22305,16 @@
         <v>75</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="P180" s="2"/>
       <c r="Q180" t="s" s="2">
@@ -22356,7 +22364,7 @@
         <v>75</v>
       </c>
       <c r="AG180" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="AH180" t="s" s="2">
         <v>76</v>
@@ -22373,13 +22381,13 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D181" s="2"/>
       <c r="E181" t="s" s="2">
@@ -22476,13 +22484,13 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D182" s="2"/>
       <c r="E182" t="s" s="2">
@@ -22581,17 +22589,17 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="D183" s="2"/>
       <c r="E183" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F183" s="2"/>
       <c r="G183" t="s" s="2">
@@ -22613,10 +22621,10 @@
         <v>88</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O183" t="s" s="2">
         <v>137</v>
@@ -22671,7 +22679,7 @@
         <v>75</v>
       </c>
       <c r="AG183" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AH183" t="s" s="2">
         <v>76</v>
@@ -22688,13 +22696,13 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D184" s="2"/>
       <c r="E184" t="s" s="2">
@@ -22720,13 +22728,13 @@
         <v>95</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="P184" s="2"/>
       <c r="Q184" t="s" s="2">
@@ -22776,7 +22784,7 @@
         <v>75</v>
       </c>
       <c r="AG184" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="AH184" t="s" s="2">
         <v>76</v>
@@ -22793,13 +22801,13 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="D185" s="2"/>
       <c r="E185" t="s" s="2">
@@ -22825,13 +22833,13 @@
         <v>238</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="P185" s="2"/>
       <c r="Q185" t="s" s="2">
@@ -22881,7 +22889,7 @@
         <v>75</v>
       </c>
       <c r="AG185" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="AH185" t="s" s="2">
         <v>82</v>
@@ -22898,13 +22906,13 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="D186" s="2"/>
       <c r="E186" t="s" s="2">
@@ -22927,16 +22935,16 @@
         <v>75</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="P186" s="2"/>
       <c r="Q186" t="s" s="2">
@@ -22986,7 +22994,7 @@
         <v>75</v>
       </c>
       <c r="AG186" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="AH186" t="s" s="2">
         <v>76</v>
@@ -23003,13 +23011,13 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="D187" s="2"/>
       <c r="E187" t="s" s="2">
@@ -23032,23 +23040,23 @@
         <v>75</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="P187" s="2"/>
       <c r="Q187" t="s" s="2">
         <v>75</v>
       </c>
       <c r="R187" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="S187" t="s" s="2">
         <v>75</v>
@@ -23093,7 +23101,7 @@
         <v>75</v>
       </c>
       <c r="AG187" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AH187" t="s" s="2">
         <v>76</v>
@@ -23110,13 +23118,13 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="D188" s="2"/>
       <c r="E188" t="s" s="2">
@@ -23139,16 +23147,16 @@
         <v>75</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="P188" s="2"/>
       <c r="Q188" t="s" s="2">
@@ -23198,7 +23206,7 @@
         <v>75</v>
       </c>
       <c r="AG188" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AH188" t="s" s="2">
         <v>76</v>
@@ -23215,13 +23223,13 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="D189" s="2"/>
       <c r="E189" t="s" s="2">
@@ -23318,13 +23326,13 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D190" s="2"/>
       <c r="E190" t="s" s="2">
@@ -23423,17 +23431,17 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="D191" s="2"/>
       <c r="E191" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F191" s="2"/>
       <c r="G191" t="s" s="2">
@@ -23455,10 +23463,10 @@
         <v>88</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O191" t="s" s="2">
         <v>137</v>
@@ -23513,7 +23521,7 @@
         <v>75</v>
       </c>
       <c r="AG191" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AH191" t="s" s="2">
         <v>76</v>
@@ -23530,13 +23538,13 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D192" s="2"/>
       <c r="E192" t="s" s="2">
@@ -23562,13 +23570,13 @@
         <v>83</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="P192" s="2"/>
       <c r="Q192" t="s" s="2">
@@ -23618,7 +23626,7 @@
         <v>75</v>
       </c>
       <c r="AG192" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="AH192" t="s" s="2">
         <v>82</v>
@@ -23635,13 +23643,13 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D193" s="2"/>
       <c r="E193" t="s" s="2">
@@ -23664,13 +23672,13 @@
         <v>75</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" s="2"/>
@@ -23721,7 +23729,7 @@
         <v>75</v>
       </c>
       <c r="AG193" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AH193" t="s" s="2">
         <v>76</v>
@@ -23738,13 +23746,13 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D194" s="2"/>
       <c r="E194" t="s" s="2">
@@ -23767,13 +23775,13 @@
         <v>75</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" s="2"/>
@@ -23824,7 +23832,7 @@
         <v>75</v>
       </c>
       <c r="AG194" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AH194" t="s" s="2">
         <v>76</v>
@@ -23836,18 +23844,18 @@
         <v>75</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D195" s="2"/>
       <c r="E195" t="s" s="2">
@@ -23944,13 +23952,13 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D196" s="2"/>
       <c r="E196" t="s" s="2">
@@ -24049,17 +24057,17 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="D197" s="2"/>
       <c r="E197" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F197" s="2"/>
       <c r="G197" t="s" s="2">
@@ -24081,10 +24089,10 @@
         <v>88</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O197" t="s" s="2">
         <v>137</v>
@@ -24139,7 +24147,7 @@
         <v>75</v>
       </c>
       <c r="AG197" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AH197" t="s" s="2">
         <v>76</v>
@@ -24156,13 +24164,13 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="D198" s="2"/>
       <c r="E198" t="s" s="2">
@@ -24188,10 +24196,10 @@
         <v>95</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" s="2"/>
@@ -24242,7 +24250,7 @@
         <v>75</v>
       </c>
       <c r="AG198" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="AH198" t="s" s="2">
         <v>76</v>
@@ -24259,13 +24267,13 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="D199" s="2"/>
       <c r="E199" t="s" s="2">
@@ -24288,23 +24296,23 @@
         <v>75</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="O199" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="P199" s="2"/>
       <c r="Q199" t="s" s="2">
         <v>75</v>
       </c>
       <c r="R199" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="S199" t="s" s="2">
         <v>75</v>
@@ -24349,7 +24357,7 @@
         <v>75</v>
       </c>
       <c r="AG199" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="AH199" t="s" s="2">
         <v>76</v>
@@ -24366,13 +24374,13 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="D200" s="2"/>
       <c r="E200" t="s" s="2">
@@ -24395,16 +24403,16 @@
         <v>75</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="O200" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="P200" s="2"/>
       <c r="Q200" t="s" s="2">
@@ -24454,7 +24462,7 @@
         <v>75</v>
       </c>
       <c r="AG200" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="AH200" t="s" s="2">
         <v>76</v>
@@ -24471,13 +24479,13 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="D201" s="2"/>
       <c r="E201" t="s" s="2">
@@ -24503,13 +24511,13 @@
         <v>83</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="P201" s="2"/>
       <c r="Q201" t="s" s="2">
@@ -24559,7 +24567,7 @@
         <v>75</v>
       </c>
       <c r="AG201" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="AH201" t="s" s="2">
         <v>76</v>
@@ -24576,13 +24584,13 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="D202" s="2"/>
       <c r="E202" t="s" s="2">
@@ -24608,10 +24616,10 @@
         <v>189</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="N202" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="O202" s="2"/>
       <c r="P202" s="2"/>
@@ -24662,7 +24670,7 @@
         <v>75</v>
       </c>
       <c r="AG202" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="AH202" t="s" s="2">
         <v>76</v>
@@ -24671,7 +24679,7 @@
         <v>82</v>
       </c>
       <c r="AJ202" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="AK202" t="s" s="2">
         <v>103</v>
@@ -24679,13 +24687,13 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="D203" s="2"/>
       <c r="E203" t="s" s="2">
@@ -24711,10 +24719,10 @@
         <v>83</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="O203" s="2"/>
       <c r="P203" s="2"/>
@@ -24765,7 +24773,7 @@
         <v>75</v>
       </c>
       <c r="AG203" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="AH203" t="s" s="2">
         <v>76</v>
@@ -24774,7 +24782,7 @@
         <v>82</v>
       </c>
       <c r="AJ203" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="AK203" t="s" s="2">
         <v>103</v>
@@ -24782,13 +24790,13 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="D204" s="2"/>
       <c r="E204" t="s" s="2">
@@ -24814,13 +24822,13 @@
         <v>78</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="O204" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="P204" s="2"/>
       <c r="Q204" t="s" s="2">
@@ -24870,7 +24878,7 @@
         <v>75</v>
       </c>
       <c r="AG204" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="AH204" t="s" s="2">
         <v>76</v>
@@ -24887,13 +24895,13 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="D205" s="2"/>
       <c r="E205" t="s" s="2">
@@ -24919,13 +24927,13 @@
         <v>78</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="O205" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="P205" s="2"/>
       <c r="Q205" t="s" s="2">
@@ -24975,7 +24983,7 @@
         <v>75</v>
       </c>
       <c r="AG205" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="AH205" t="s" s="2">
         <v>76</v>
@@ -24992,7 +25000,7 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>30</v>
@@ -25095,7 +25103,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>81</v>
@@ -25198,7 +25206,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>87</v>
@@ -25301,7 +25309,7 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B209" t="s" s="2">
         <v>94</v>
@@ -25347,7 +25355,7 @@
       </c>
       <c r="R209" s="2"/>
       <c r="S209" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="T209" t="s" s="2">
         <v>75</v>
@@ -25406,7 +25414,7 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B210" t="s" s="2">
         <v>99</v>
@@ -25509,7 +25517,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>30</v>
@@ -25612,7 +25620,7 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B212" t="s" s="2">
         <v>81</v>
@@ -25715,7 +25723,7 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B213" t="s" s="2">
         <v>87</v>
@@ -25818,7 +25826,7 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B214" t="s" s="2">
         <v>94</v>
@@ -25864,7 +25872,7 @@
       </c>
       <c r="R214" s="2"/>
       <c r="S214" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="T214" t="s" s="2">
         <v>75</v>
@@ -25923,7 +25931,7 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B215" t="s" s="2">
         <v>99</v>

--- a/ig/improve-doc/all-profiles.xlsx
+++ b/ig/improve-doc/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-02T16:50:25+00:00</t>
+    <t>2024-12-04T07:44:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
